--- a/VerveStacks_ESP_grids_kan/vt_vervestacks_ESP_v1.xlsx
+++ b/VerveStacks_ESP_grids_kan/vt_vervestacks_ESP_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50096A6C-A4FE-439C-BC25-57DEB1029A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{825B79CB-E644-4D64-B88B-F93F14DB7BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{329240A8-688A-4100-95C2-A915DC3C3BF1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{77CA735F-5499-4864-BAE6-68555465731D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4993,7 +4993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{094B15E2-9594-4A14-9D9F-DB793337FEEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C32B288B-6995-4C8D-85F0-DC585F055075}">
   <dimension ref="B9:V160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14373,7 +14373,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BDFFB88-2DFA-43FA-8DDF-347C81F34B98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B4B594-F8DA-4DA7-819C-6BA9AED9C2F3}">
   <dimension ref="B9:V235"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27908,7 +27908,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738AC7F9-A167-419C-9DEB-DFBABD5438D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{993813AE-85C5-4B09-9410-3B73CF9B4901}">
   <dimension ref="B9:V845"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -28793,7 +28793,7 @@
         <v>14</v>
       </c>
       <c r="R24" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S24" t="s">
         <v>580</v>
@@ -28852,7 +28852,7 @@
         <v>14</v>
       </c>
       <c r="R25" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="S25" t="s">
         <v>580</v>
@@ -46712,7 +46712,7 @@
         <v>14</v>
       </c>
       <c r="R336" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S336" t="s">
         <v>580</v>
@@ -46771,7 +46771,7 @@
         <v>14</v>
       </c>
       <c r="R337" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="S337" t="s">
         <v>580</v>
@@ -46948,7 +46948,7 @@
         <v>14</v>
       </c>
       <c r="R340" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S340" t="s">
         <v>580</v>
@@ -47007,7 +47007,7 @@
         <v>14</v>
       </c>
       <c r="R341" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="S341" t="s">
         <v>580</v>
@@ -47361,7 +47361,7 @@
         <v>14</v>
       </c>
       <c r="R347" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="S347" t="s">
         <v>580</v>
@@ -47420,7 +47420,7 @@
         <v>14</v>
       </c>
       <c r="R348" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S348" t="s">
         <v>580</v>
@@ -47479,7 +47479,7 @@
         <v>14</v>
       </c>
       <c r="R349" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S349" t="s">
         <v>580</v>
@@ -47532,7 +47532,7 @@
         <v>14</v>
       </c>
       <c r="R350" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="S350" t="s">
         <v>580</v>
@@ -47948,7 +47948,7 @@
         <v>14</v>
       </c>
       <c r="R357" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S357" t="s">
         <v>580</v>
@@ -48010,7 +48010,7 @@
         <v>14</v>
       </c>
       <c r="R358" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="S358" t="s">
         <v>580</v>
@@ -48072,7 +48072,7 @@
         <v>14</v>
       </c>
       <c r="R359" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S359" t="s">
         <v>580</v>
@@ -48134,7 +48134,7 @@
         <v>14</v>
       </c>
       <c r="R360" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="S360" t="s">
         <v>580</v>
@@ -48630,7 +48630,7 @@
         <v>14</v>
       </c>
       <c r="R368" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="S368" t="s">
         <v>580</v>
@@ -48692,7 +48692,7 @@
         <v>14</v>
       </c>
       <c r="R369" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S369" t="s">
         <v>580</v>
@@ -51420,7 +51420,7 @@
         <v>14</v>
       </c>
       <c r="R413" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="S413" t="s">
         <v>580</v>
@@ -51482,7 +51482,7 @@
         <v>14</v>
       </c>
       <c r="R414" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S414" t="s">
         <v>580</v>
@@ -68526,7 +68526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B70698D2-A06A-4D5B-B17B-F87E09BFC5A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA643DF-713F-4911-95C8-969CC79C085E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
